--- a/Exp3_PTO_GRPO/eda/results/lookahead/replication/tables/replication.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/lookahead/replication/tables/replication.xlsx
@@ -2059,77 +2059,77 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>n_Cooperative</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>mean_Cooperative</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>sd_Cooperative</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>share_ge45_Cooperative</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>share_eq5_Cooperative</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>n_WarmsUp</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>mean_WarmsUp</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>sd_WarmsUp</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>share_ge45_WarmsUp</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>share_eq5_WarmsUp</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>n_Resistant</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>mean_Resistant</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>sd_Resistant</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>share_ge45_Resistant</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>share_eq5_Resistant</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>n_WarmsUp</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>mean_WarmsUp</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>sd_WarmsUp</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>share_ge45_WarmsUp</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>share_eq5_WarmsUp</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>n_Cooperative</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>mean_Cooperative</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>sd_Cooperative</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>share_ge45_Cooperative</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>share_eq5_Cooperative</t>
         </is>
       </c>
     </row>
@@ -2166,10 +2166,10 @@
         <v>32</v>
       </c>
       <c r="J2" t="n">
-        <v>1.254963235294118</v>
+        <v>2.499632352941177</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1852503449697697</v>
+        <v>0.5431609878199887</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -2196,10 +2196,10 @@
         <v>32</v>
       </c>
       <c r="T2" t="n">
-        <v>2.499632352941177</v>
+        <v>1.254963235294118</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5431609878199887</v>
+        <v>0.1852503449697697</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -2241,10 +2241,10 @@
         <v>32</v>
       </c>
       <c r="J3" t="n">
-        <v>1.520036764705882</v>
+        <v>2.838051470588235</v>
       </c>
       <c r="K3" t="n">
-        <v>0.404177480869443</v>
+        <v>0.4852414654319315</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -2271,10 +2271,10 @@
         <v>32</v>
       </c>
       <c r="T3" t="n">
-        <v>2.838051470588235</v>
+        <v>1.520036764705882</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4852414654319315</v>
+        <v>0.404177480869443</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -2316,10 +2316,10 @@
         <v>32</v>
       </c>
       <c r="J4" t="n">
-        <v>1.479963235294118</v>
+        <v>2.734007352941177</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3466641675144819</v>
+        <v>0.4791319642513091</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2346,10 +2346,10 @@
         <v>32</v>
       </c>
       <c r="T4" t="n">
-        <v>2.734007352941177</v>
+        <v>1.479963235294118</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4791319642513091</v>
+        <v>0.3466641675144819</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -2391,10 +2391,10 @@
         <v>32</v>
       </c>
       <c r="J5" t="n">
-        <v>1.983088235294118</v>
+        <v>3.161948529411765</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2725887192997844</v>
+        <v>0.4239718971889325</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2421,10 +2421,10 @@
         <v>32</v>
       </c>
       <c r="T5" t="n">
-        <v>3.161948529411765</v>
+        <v>1.983088235294118</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4239718971889325</v>
+        <v>0.2725887192997844</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>32</v>
       </c>
       <c r="J6" t="n">
-        <v>1.791360294117647</v>
+        <v>2.984191176470588</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3493044269832891</v>
+        <v>0.7116454139686992</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2496,10 +2496,10 @@
         <v>32</v>
       </c>
       <c r="T6" t="n">
-        <v>2.984191176470588</v>
+        <v>1.791360294117647</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7116454139686992</v>
+        <v>0.3493044269832891</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -2541,10 +2541,10 @@
         <v>32</v>
       </c>
       <c r="J7" t="n">
-        <v>1.706433823529412</v>
+        <v>3.179595588235294</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3347839234810477</v>
+        <v>0.6808397544471305</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2571,10 +2571,10 @@
         <v>32</v>
       </c>
       <c r="T7" t="n">
-        <v>3.179595588235294</v>
+        <v>1.706433823529412</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6808397544471305</v>
+        <v>0.3347839234810477</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -2616,10 +2616,10 @@
         <v>32</v>
       </c>
       <c r="J8" t="n">
-        <v>1.795220588235294</v>
+        <v>2.788051470588235</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4260478504170164</v>
+        <v>1.044352390294241</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2646,10 +2646,10 @@
         <v>32</v>
       </c>
       <c r="T8" t="n">
-        <v>2.788051470588235</v>
+        <v>1.795220588235294</v>
       </c>
       <c r="U8" t="n">
-        <v>1.044352390294241</v>
+        <v>0.4260478504170164</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -2691,10 +2691,10 @@
         <v>32</v>
       </c>
       <c r="J9" t="n">
-        <v>1.834926470588235</v>
+        <v>3.202573529411765</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4164920756364716</v>
+        <v>0.7940353285045141</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>32</v>
       </c>
       <c r="T9" t="n">
-        <v>3.202573529411765</v>
+        <v>1.834926470588235</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7940353285045141</v>
+        <v>0.4164920756364716</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2766,10 +2766,10 @@
         <v>32</v>
       </c>
       <c r="J10" t="n">
-        <v>1.901838235294118</v>
+        <v>3.462867647058824</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2763168755946037</v>
+        <v>0.4094934309157663</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2796,10 +2796,10 @@
         <v>32</v>
       </c>
       <c r="T10" t="n">
-        <v>3.462867647058824</v>
+        <v>1.901838235294118</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4094934309157663</v>
+        <v>0.2763168755946037</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2841,10 +2841,10 @@
         <v>32</v>
       </c>
       <c r="J11" t="n">
-        <v>1.582720588235294</v>
+        <v>2.709742647058824</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3938837491672129</v>
+        <v>1.024443537543197</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2871,10 +2871,10 @@
         <v>32</v>
       </c>
       <c r="T11" t="n">
-        <v>2.709742647058824</v>
+        <v>1.582720588235294</v>
       </c>
       <c r="U11" t="n">
-        <v>1.024443537543197</v>
+        <v>0.3938837491672129</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2916,10 +2916,10 @@
         <v>32</v>
       </c>
       <c r="J12" t="n">
-        <v>1.80625</v>
+        <v>2.760661764705882</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3160651363930065</v>
+        <v>0.4750533834801439</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2946,10 +2946,10 @@
         <v>32</v>
       </c>
       <c r="T12" t="n">
-        <v>2.760661764705882</v>
+        <v>1.80625</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4750533834801439</v>
+        <v>0.3160651363930065</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2991,10 +2991,10 @@
         <v>32</v>
       </c>
       <c r="J13" t="n">
-        <v>1.306066176470588</v>
+        <v>2.510294117647059</v>
       </c>
       <c r="K13" t="n">
-        <v>0.256912404185725</v>
+        <v>0.4884512907823101</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3021,10 +3021,10 @@
         <v>32</v>
       </c>
       <c r="T13" t="n">
-        <v>2.510294117647059</v>
+        <v>1.306066176470588</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4884512907823101</v>
+        <v>0.256912404185725</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -3066,10 +3066,10 @@
         <v>32</v>
       </c>
       <c r="J14" t="n">
-        <v>1.465073529411765</v>
+        <v>2.759191176470588</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3475615870811626</v>
+        <v>0.5812755976814034</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3096,10 +3096,10 @@
         <v>32</v>
       </c>
       <c r="T14" t="n">
-        <v>2.759191176470588</v>
+        <v>1.465073529411765</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5812755976814034</v>
+        <v>0.3475615870811626</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3141,10 +3141,10 @@
         <v>32</v>
       </c>
       <c r="J15" t="n">
-        <v>1.573161764705882</v>
+        <v>2.814522058823529</v>
       </c>
       <c r="K15" t="n">
-        <v>0.367106433624721</v>
+        <v>0.5419596353975707</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>32</v>
       </c>
       <c r="T15" t="n">
-        <v>2.814522058823529</v>
+        <v>1.573161764705882</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5419596353975707</v>
+        <v>0.367106433624721</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3216,10 +3216,10 @@
         <v>32</v>
       </c>
       <c r="J16" t="n">
-        <v>1.840992647058823</v>
+        <v>3.190808823529412</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3629248437087863</v>
+        <v>0.421735970640163</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3246,10 +3246,10 @@
         <v>32</v>
       </c>
       <c r="T16" t="n">
-        <v>3.190808823529412</v>
+        <v>1.840992647058823</v>
       </c>
       <c r="U16" t="n">
-        <v>0.421735970640163</v>
+        <v>0.3629248437087863</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3291,10 +3291,10 @@
         <v>32</v>
       </c>
       <c r="J17" t="n">
-        <v>2.119669117647059</v>
+        <v>3.297058823529412</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3311070816013302</v>
+        <v>0.3707704139422326</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3321,10 +3321,10 @@
         <v>32</v>
       </c>
       <c r="T17" t="n">
-        <v>3.297058823529412</v>
+        <v>2.119669117647059</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3707704139422326</v>
+        <v>0.3311070816013302</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3366,10 +3366,10 @@
         <v>32</v>
       </c>
       <c r="J18" t="n">
-        <v>1.890992647058823</v>
+        <v>3.452205882352941</v>
       </c>
       <c r="K18" t="n">
-        <v>0.450096997830678</v>
+        <v>0.2781982034963909</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3396,10 +3396,10 @@
         <v>32</v>
       </c>
       <c r="T18" t="n">
-        <v>3.452205882352941</v>
+        <v>1.890992647058823</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2781982034963909</v>
+        <v>0.450096997830678</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>32</v>
       </c>
       <c r="J19" t="n">
-        <v>1.309742647058823</v>
+        <v>2.384742647058824</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3197506052346744</v>
+        <v>0.7013164464523245</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -3471,10 +3471,10 @@
         <v>32</v>
       </c>
       <c r="T19" t="n">
-        <v>2.384742647058824</v>
+        <v>1.309742647058823</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7013164464523245</v>
+        <v>0.3197506052346744</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -3516,10 +3516,10 @@
         <v>32</v>
       </c>
       <c r="J20" t="n">
-        <v>1.464522058823529</v>
+        <v>2.897058823529412</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3602608608746048</v>
+        <v>0.5358224554473063</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>32</v>
       </c>
       <c r="T20" t="n">
-        <v>2.897058823529412</v>
+        <v>1.464522058823529</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5358224554473063</v>
+        <v>0.3602608608746048</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -3591,10 +3591,10 @@
         <v>32</v>
       </c>
       <c r="J21" t="n">
-        <v>1.560477941176471</v>
+        <v>2.967279411764705</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5124877319062303</v>
+        <v>0.4739984064744608</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -3621,10 +3621,10 @@
         <v>32</v>
       </c>
       <c r="T21" t="n">
-        <v>2.967279411764705</v>
+        <v>1.560477941176471</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4739984064744608</v>
+        <v>0.5124877319062303</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -3666,10 +3666,10 @@
         <v>32</v>
       </c>
       <c r="J22" t="n">
-        <v>1.887683823529412</v>
+        <v>3.089889705882353</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4568471992791778</v>
+        <v>0.5633943387003125</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -3696,10 +3696,10 @@
         <v>32</v>
       </c>
       <c r="T22" t="n">
-        <v>3.089889705882353</v>
+        <v>1.887683823529412</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5633943387003125</v>
+        <v>0.4568471992791778</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3741,10 +3741,10 @@
         <v>32</v>
       </c>
       <c r="J23" t="n">
-        <v>2.006617647058824</v>
+        <v>3.292279411764706</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4107326453416197</v>
+        <v>0.393754789204721</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>32</v>
       </c>
       <c r="T23" t="n">
-        <v>3.292279411764706</v>
+        <v>2.006617647058824</v>
       </c>
       <c r="U23" t="n">
-        <v>0.393754789204721</v>
+        <v>0.4107326453416197</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -3816,10 +3816,10 @@
         <v>32</v>
       </c>
       <c r="J24" t="n">
-        <v>2.038419117647059</v>
+        <v>3.360845588235294</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3947924902223636</v>
+        <v>0.3370542348952984</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3846,10 +3846,10 @@
         <v>32</v>
       </c>
       <c r="T24" t="n">
-        <v>3.360845588235294</v>
+        <v>2.038419117647059</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3370542348952984</v>
+        <v>0.3947924902223636</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>2.106066176470588</v>
+        <v>3.421875</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3641284661327611</v>
+        <v>0.4210639667593708</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3921,10 +3921,10 @@
         <v>32</v>
       </c>
       <c r="T25" t="n">
-        <v>3.421875</v>
+        <v>2.106066176470588</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4210639667593708</v>
+        <v>0.3641284661327611</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3966,10 +3966,10 @@
         <v>32</v>
       </c>
       <c r="J26" t="n">
-        <v>2.155514705882353</v>
+        <v>3.458088235294118</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3669756677932695</v>
+        <v>0.5122666517027061</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3996,10 +3996,10 @@
         <v>32</v>
       </c>
       <c r="T26" t="n">
-        <v>3.458088235294118</v>
+        <v>2.155514705882353</v>
       </c>
       <c r="U26" t="n">
-        <v>0.5122666517027061</v>
+        <v>0.3669756677932695</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -4041,10 +4041,10 @@
         <v>32</v>
       </c>
       <c r="J27" t="n">
-        <v>2.188235294117647</v>
+        <v>3.522058823529412</v>
       </c>
       <c r="K27" t="n">
-        <v>0.342935334101601</v>
+        <v>0.5370210066265655</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -4071,10 +4071,10 @@
         <v>32</v>
       </c>
       <c r="T27" t="n">
-        <v>3.522058823529412</v>
+        <v>2.188235294117647</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5370210066265655</v>
+        <v>0.342935334101601</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -4116,10 +4116,10 @@
         <v>32</v>
       </c>
       <c r="J28" t="n">
-        <v>2.136580882352941</v>
+        <v>3.634007352941176</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2951206214659038</v>
+        <v>0.1821461419967851</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -4146,10 +4146,10 @@
         <v>32</v>
       </c>
       <c r="T28" t="n">
-        <v>3.634007352941176</v>
+        <v>2.136580882352941</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1821461419967851</v>
+        <v>0.2951206214659038</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>32</v>
       </c>
       <c r="J29" t="n">
-        <v>2.212132352941176</v>
+        <v>3.666360294117647</v>
       </c>
       <c r="K29" t="n">
-        <v>0.248185456385433</v>
+        <v>0.192997367523414</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -4221,10 +4221,10 @@
         <v>32</v>
       </c>
       <c r="T29" t="n">
-        <v>3.666360294117647</v>
+        <v>2.212132352941176</v>
       </c>
       <c r="U29" t="n">
-        <v>0.192997367523414</v>
+        <v>0.248185456385433</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -4266,10 +4266,10 @@
         <v>32</v>
       </c>
       <c r="J30" t="n">
-        <v>1.413786764705882</v>
+        <v>2.311948529411765</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4198278296806853</v>
+        <v>0.6561199004394326</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -4296,10 +4296,10 @@
         <v>32</v>
       </c>
       <c r="T30" t="n">
-        <v>2.311948529411765</v>
+        <v>1.413786764705882</v>
       </c>
       <c r="U30" t="n">
-        <v>0.6561199004394326</v>
+        <v>0.4198278296806853</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -4341,10 +4341,10 @@
         <v>32</v>
       </c>
       <c r="J31" t="n">
-        <v>1.509558823529412</v>
+        <v>2.726286764705882</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4455701519993434</v>
+        <v>0.6416002018459922</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -4371,10 +4371,10 @@
         <v>32</v>
       </c>
       <c r="T31" t="n">
-        <v>2.726286764705882</v>
+        <v>1.509558823529412</v>
       </c>
       <c r="U31" t="n">
-        <v>0.6416002018459922</v>
+        <v>0.4455701519993434</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -4416,10 +4416,10 @@
         <v>32</v>
       </c>
       <c r="J32" t="n">
-        <v>1.475919117647059</v>
+        <v>2.715073529411765</v>
       </c>
       <c r="K32" t="n">
-        <v>0.3531288538802727</v>
+        <v>0.4749511639143365</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -4446,10 +4446,10 @@
         <v>32</v>
       </c>
       <c r="T32" t="n">
-        <v>2.715073529411765</v>
+        <v>1.475919117647059</v>
       </c>
       <c r="U32" t="n">
-        <v>0.4749511639143365</v>
+        <v>0.3531288538802727</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -4491,10 +4491,10 @@
         <v>32</v>
       </c>
       <c r="J33" t="n">
-        <v>1.689338235294118</v>
+        <v>2.987316176470588</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4519270479875673</v>
+        <v>0.5718771205016261</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4521,10 +4521,10 @@
         <v>32</v>
       </c>
       <c r="T33" t="n">
-        <v>2.987316176470588</v>
+        <v>1.689338235294118</v>
       </c>
       <c r="U33" t="n">
-        <v>0.5718771205016261</v>
+        <v>0.4519270479875673</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -4566,10 +4566,10 @@
         <v>32</v>
       </c>
       <c r="J34" t="n">
-        <v>1.794301470588235</v>
+        <v>3.236029411764706</v>
       </c>
       <c r="K34" t="n">
-        <v>0.433646001369609</v>
+        <v>0.4429546706744966</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4596,10 +4596,10 @@
         <v>32</v>
       </c>
       <c r="T34" t="n">
-        <v>3.236029411764706</v>
+        <v>1.794301470588235</v>
       </c>
       <c r="U34" t="n">
-        <v>0.4429546706744966</v>
+        <v>0.433646001369609</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -4641,10 +4641,10 @@
         <v>32</v>
       </c>
       <c r="J35" t="n">
-        <v>1.876654411764706</v>
+        <v>3.21452205882353</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3900036902267021</v>
+        <v>0.4261409689347189</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4671,10 +4671,10 @@
         <v>32</v>
       </c>
       <c r="T35" t="n">
-        <v>3.21452205882353</v>
+        <v>1.876654411764706</v>
       </c>
       <c r="U35" t="n">
-        <v>0.4261409689347189</v>
+        <v>0.3900036902267021</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4716,10 +4716,10 @@
         <v>32</v>
       </c>
       <c r="J36" t="n">
-        <v>1.788602941176471</v>
+        <v>3.127205882352941</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4368681155893315</v>
+        <v>0.5890066100604845</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -4746,10 +4746,10 @@
         <v>32</v>
       </c>
       <c r="T36" t="n">
-        <v>3.127205882352941</v>
+        <v>1.788602941176471</v>
       </c>
       <c r="U36" t="n">
-        <v>0.5890066100604845</v>
+        <v>0.4368681155893315</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4791,10 +4791,10 @@
         <v>32</v>
       </c>
       <c r="J37" t="n">
-        <v>2.009375</v>
+        <v>3.417830882352941</v>
       </c>
       <c r="K37" t="n">
-        <v>0.474372496319064</v>
+        <v>0.3325698587681162</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -4821,10 +4821,10 @@
         <v>32</v>
       </c>
       <c r="T37" t="n">
-        <v>3.417830882352941</v>
+        <v>2.009375</v>
       </c>
       <c r="U37" t="n">
-        <v>0.3325698587681162</v>
+        <v>0.474372496319064</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -4866,10 +4866,10 @@
         <v>32</v>
       </c>
       <c r="J38" t="n">
-        <v>1.929595588235294</v>
+        <v>3.315073529411765</v>
       </c>
       <c r="K38" t="n">
-        <v>0.3287553923389903</v>
+        <v>0.5241823476698367</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -4896,10 +4896,10 @@
         <v>32</v>
       </c>
       <c r="T38" t="n">
-        <v>3.315073529411765</v>
+        <v>1.929595588235294</v>
       </c>
       <c r="U38" t="n">
-        <v>0.5241823476698367</v>
+        <v>0.3287553923389903</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -4941,10 +4941,10 @@
         <v>32</v>
       </c>
       <c r="J39" t="n">
-        <v>2.096139705882353</v>
+        <v>3.210294117647059</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5471141335713025</v>
+        <v>0.5998511554038694</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -4971,10 +4971,10 @@
         <v>32</v>
       </c>
       <c r="T39" t="n">
-        <v>3.210294117647059</v>
+        <v>2.096139705882353</v>
       </c>
       <c r="U39" t="n">
-        <v>0.5998511554038694</v>
+        <v>0.5471141335713025</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -5016,10 +5016,10 @@
         <v>32</v>
       </c>
       <c r="J40" t="n">
-        <v>2.113419117647059</v>
+        <v>3.095404411764706</v>
       </c>
       <c r="K40" t="n">
-        <v>0.4228996856900155</v>
+        <v>0.6671651612061803</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -5046,10 +5046,10 @@
         <v>32</v>
       </c>
       <c r="T40" t="n">
-        <v>3.095404411764706</v>
+        <v>2.113419117647059</v>
       </c>
       <c r="U40" t="n">
-        <v>0.6671651612061803</v>
+        <v>0.4228996856900155</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -5091,13 +5091,13 @@
         <v>32</v>
       </c>
       <c r="J41" t="n">
-        <v>1.780882352941177</v>
+        <v>4.371874999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>0.4727110563848076</v>
+        <v>0.4536779890735723</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>0.34375</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -5121,13 +5121,13 @@
         <v>32</v>
       </c>
       <c r="T41" t="n">
-        <v>4.371874999999999</v>
+        <v>1.780882352941177</v>
       </c>
       <c r="U41" t="n">
-        <v>0.4536779890735723</v>
+        <v>0.4727110563848076</v>
       </c>
       <c r="V41" t="n">
-        <v>0.34375</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -5166,13 +5166,13 @@
         <v>32</v>
       </c>
       <c r="J42" t="n">
-        <v>2.404779411764706</v>
+        <v>4.527205882352941</v>
       </c>
       <c r="K42" t="n">
-        <v>0.7463636405968014</v>
+        <v>0.1812985985283091</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>0.4375</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>32</v>
       </c>
       <c r="T42" t="n">
-        <v>4.527205882352941</v>
+        <v>2.404779411764706</v>
       </c>
       <c r="U42" t="n">
-        <v>0.1812985985283091</v>
+        <v>0.7463636405968014</v>
       </c>
       <c r="V42" t="n">
-        <v>0.4375</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -5241,13 +5241,13 @@
         <v>32</v>
       </c>
       <c r="J43" t="n">
-        <v>2.2625</v>
+        <v>4.581433823529412</v>
       </c>
       <c r="K43" t="n">
-        <v>0.6063744984493362</v>
+        <v>0.233265014461578</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>0.65625</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -5271,13 +5271,13 @@
         <v>32</v>
       </c>
       <c r="T43" t="n">
-        <v>4.581433823529412</v>
+        <v>2.2625</v>
       </c>
       <c r="U43" t="n">
-        <v>0.233265014461578</v>
+        <v>0.6063744984493362</v>
       </c>
       <c r="V43" t="n">
-        <v>0.65625</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -5316,13 +5316,13 @@
         <v>32</v>
       </c>
       <c r="J44" t="n">
-        <v>3.068933823529412</v>
+        <v>4.73952205882353</v>
       </c>
       <c r="K44" t="n">
-        <v>0.5478799297304984</v>
+        <v>0.1307779736440559</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>0.90625</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5346,13 +5346,13 @@
         <v>32</v>
       </c>
       <c r="T44" t="n">
-        <v>4.73952205882353</v>
+        <v>3.068933823529412</v>
       </c>
       <c r="U44" t="n">
-        <v>0.1307779736440559</v>
+        <v>0.5478799297304984</v>
       </c>
       <c r="V44" t="n">
-        <v>0.90625</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -5391,13 +5391,13 @@
         <v>32</v>
       </c>
       <c r="J45" t="n">
-        <v>3.19172794117647</v>
+        <v>4.684007352941177</v>
       </c>
       <c r="K45" t="n">
-        <v>0.5548130521914729</v>
+        <v>0.2195045328149992</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>0.71875</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5421,13 +5421,13 @@
         <v>32</v>
       </c>
       <c r="T45" t="n">
-        <v>4.684007352941177</v>
+        <v>3.19172794117647</v>
       </c>
       <c r="U45" t="n">
-        <v>0.2195045328149992</v>
+        <v>0.5548130521914729</v>
       </c>
       <c r="V45" t="n">
-        <v>0.71875</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -5466,13 +5466,13 @@
         <v>32</v>
       </c>
       <c r="J46" t="n">
-        <v>3.062683823529412</v>
+        <v>4.76672794117647</v>
       </c>
       <c r="K46" t="n">
-        <v>0.6107413886504608</v>
+        <v>0.2118153501269246</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5496,13 +5496,13 @@
         <v>32</v>
       </c>
       <c r="T46" t="n">
-        <v>4.76672794117647</v>
+        <v>3.062683823529412</v>
       </c>
       <c r="U46" t="n">
-        <v>0.2118153501269246</v>
+        <v>0.6107413886504608</v>
       </c>
       <c r="V46" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
         <v>0</v>
@@ -5541,13 +5541,13 @@
         <v>32</v>
       </c>
       <c r="J47" t="n">
-        <v>3.209742647058824</v>
+        <v>4.566544117647059</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5226248701881373</v>
+        <v>0.5162769462750113</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5571,13 +5571,13 @@
         <v>32</v>
       </c>
       <c r="T47" t="n">
-        <v>4.566544117647059</v>
+        <v>3.209742647058824</v>
       </c>
       <c r="U47" t="n">
-        <v>0.5162769462750113</v>
+        <v>0.5226248701881373</v>
       </c>
       <c r="V47" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
         <v>0</v>
@@ -5616,16 +5616,16 @@
         <v>32</v>
       </c>
       <c r="J48" t="n">
-        <v>3.290992647058824</v>
+        <v>4.761948529411764</v>
       </c>
       <c r="K48" t="n">
-        <v>0.6617564568324156</v>
+        <v>0.2899553078209497</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>0.84375</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>0.03125</v>
       </c>
       <c r="N48" t="n">
         <v>32</v>
@@ -5646,16 +5646,16 @@
         <v>32</v>
       </c>
       <c r="T48" t="n">
-        <v>4.761948529411764</v>
+        <v>3.290992647058824</v>
       </c>
       <c r="U48" t="n">
-        <v>0.2899553078209497</v>
+        <v>0.6617564568324156</v>
       </c>
       <c r="V48" t="n">
-        <v>0.84375</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>0.03125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -5691,16 +5691,16 @@
         <v>32</v>
       </c>
       <c r="J49" t="n">
-        <v>3.295588235294118</v>
+        <v>4.920036764705882</v>
       </c>
       <c r="K49" t="n">
-        <v>0.5969337882368428</v>
+        <v>0.04107766337012785</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>0.15625</v>
       </c>
       <c r="N49" t="n">
         <v>32</v>
@@ -5721,16 +5721,16 @@
         <v>32</v>
       </c>
       <c r="T49" t="n">
-        <v>4.920036764705882</v>
+        <v>3.295588235294118</v>
       </c>
       <c r="U49" t="n">
-        <v>0.04107766337012785</v>
+        <v>0.5969337882368428</v>
       </c>
       <c r="V49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>0.15625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -5766,13 +5766,13 @@
         <v>32</v>
       </c>
       <c r="J50" t="n">
-        <v>3.208823529411765</v>
+        <v>4.596507352941178</v>
       </c>
       <c r="K50" t="n">
-        <v>0.4748525951953363</v>
+        <v>0.4230438376458792</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>0.65625</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -5796,13 +5796,13 @@
         <v>32</v>
       </c>
       <c r="T50" t="n">
-        <v>4.596507352941178</v>
+        <v>3.208823529411765</v>
       </c>
       <c r="U50" t="n">
-        <v>0.4230438376458792</v>
+        <v>0.4748525951953363</v>
       </c>
       <c r="V50" t="n">
-        <v>0.65625</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
         <v>0</v>
@@ -5841,16 +5841,16 @@
         <v>32</v>
       </c>
       <c r="J51" t="n">
-        <v>2.845220588235294</v>
+        <v>4.736580882352941</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5829581841323825</v>
+        <v>0.6341171442915351</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>0.90625</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>0.1875</v>
       </c>
       <c r="N51" t="n">
         <v>32</v>
@@ -5871,16 +5871,16 @@
         <v>32</v>
       </c>
       <c r="T51" t="n">
-        <v>4.736580882352941</v>
+        <v>2.845220588235294</v>
       </c>
       <c r="U51" t="n">
-        <v>0.6341171442915351</v>
+        <v>0.5829581841323825</v>
       </c>
       <c r="V51" t="n">
-        <v>0.90625</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>0.1875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -5916,13 +5916,13 @@
         <v>32</v>
       </c>
       <c r="J52" t="n">
-        <v>1.887683823529412</v>
+        <v>4.371875</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5279240310018183</v>
+        <v>0.4834987417961403</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>0.40625</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -5946,13 +5946,13 @@
         <v>32</v>
       </c>
       <c r="T52" t="n">
-        <v>4.371875</v>
+        <v>1.887683823529412</v>
       </c>
       <c r="U52" t="n">
-        <v>0.4834987417961403</v>
+        <v>0.5279240310018183</v>
       </c>
       <c r="V52" t="n">
-        <v>0.40625</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
         <v>0</v>
@@ -5991,13 +5991,13 @@
         <v>32</v>
       </c>
       <c r="J53" t="n">
-        <v>2.252757352941176</v>
+        <v>4.530882352941177</v>
       </c>
       <c r="K53" t="n">
-        <v>0.7126000467295458</v>
+        <v>0.2975623702936178</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>0.53125</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6021,13 +6021,13 @@
         <v>32</v>
       </c>
       <c r="T53" t="n">
-        <v>4.530882352941177</v>
+        <v>2.252757352941176</v>
       </c>
       <c r="U53" t="n">
-        <v>0.2975623702936178</v>
+        <v>0.7126000467295458</v>
       </c>
       <c r="V53" t="n">
-        <v>0.53125</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
         <v>0</v>
@@ -6066,13 +6066,13 @@
         <v>32</v>
       </c>
       <c r="J54" t="n">
-        <v>2.554963235294117</v>
+        <v>4.559191176470588</v>
       </c>
       <c r="K54" t="n">
-        <v>0.5920438554040843</v>
+        <v>0.3704509775632157</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>0.59375</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -6096,13 +6096,13 @@
         <v>32</v>
       </c>
       <c r="T54" t="n">
-        <v>4.559191176470588</v>
+        <v>2.554963235294117</v>
       </c>
       <c r="U54" t="n">
-        <v>0.3704509775632157</v>
+        <v>0.5920438554040843</v>
       </c>
       <c r="V54" t="n">
-        <v>0.59375</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
         <v>0</v>
@@ -6141,13 +6141,13 @@
         <v>32</v>
       </c>
       <c r="J55" t="n">
-        <v>2.883455882352941</v>
+        <v>4.709007352941176</v>
       </c>
       <c r="K55" t="n">
-        <v>0.569197502107879</v>
+        <v>0.2023137973204649</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>0.8125</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6171,13 +6171,13 @@
         <v>32</v>
       </c>
       <c r="T55" t="n">
-        <v>4.709007352941176</v>
+        <v>2.883455882352941</v>
       </c>
       <c r="U55" t="n">
-        <v>0.2023137973204649</v>
+        <v>0.569197502107879</v>
       </c>
       <c r="V55" t="n">
-        <v>0.8125</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
         <v>0</v>
@@ -6216,13 +6216,13 @@
         <v>32</v>
       </c>
       <c r="J56" t="n">
-        <v>3.359742647058824</v>
+        <v>4.752389705882353</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5410384886694074</v>
+        <v>0.09864988103849653</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -6246,13 +6246,13 @@
         <v>32</v>
       </c>
       <c r="T56" t="n">
-        <v>4.752389705882353</v>
+        <v>3.359742647058824</v>
       </c>
       <c r="U56" t="n">
-        <v>0.09864988103849653</v>
+        <v>0.5410384886694074</v>
       </c>
       <c r="V56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
         <v>0</v>
@@ -6291,13 +6291,13 @@
         <v>32</v>
       </c>
       <c r="J57" t="n">
-        <v>3.037867647058824</v>
+        <v>4.796875</v>
       </c>
       <c r="K57" t="n">
-        <v>0.7686381709194494</v>
+        <v>0.1036124427157423</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -6321,13 +6321,13 @@
         <v>32</v>
       </c>
       <c r="T57" t="n">
-        <v>4.796875</v>
+        <v>3.037867647058824</v>
       </c>
       <c r="U57" t="n">
-        <v>0.1036124427157423</v>
+        <v>0.7686381709194494</v>
       </c>
       <c r="V57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
         <v>0</v>
@@ -6366,13 +6366,13 @@
         <v>32</v>
       </c>
       <c r="J58" t="n">
-        <v>1.926838235294118</v>
+        <v>4.231066176470589</v>
       </c>
       <c r="K58" t="n">
-        <v>0.5897247509130773</v>
+        <v>0.8688919244732215</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>0.53125</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -6396,13 +6396,13 @@
         <v>32</v>
       </c>
       <c r="T58" t="n">
-        <v>4.231066176470589</v>
+        <v>1.926838235294118</v>
       </c>
       <c r="U58" t="n">
-        <v>0.8688919244732215</v>
+        <v>0.5897247509130773</v>
       </c>
       <c r="V58" t="n">
-        <v>0.53125</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
         <v>0</v>
@@ -6441,13 +6441,13 @@
         <v>32</v>
       </c>
       <c r="J59" t="n">
-        <v>2.248529411764706</v>
+        <v>4.533455882352941</v>
       </c>
       <c r="K59" t="n">
-        <v>0.7490456032658157</v>
+        <v>0.2425330362883789</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -6471,13 +6471,13 @@
         <v>32</v>
       </c>
       <c r="T59" t="n">
-        <v>4.533455882352941</v>
+        <v>2.248529411764706</v>
       </c>
       <c r="U59" t="n">
-        <v>0.2425330362883789</v>
+        <v>0.7490456032658157</v>
       </c>
       <c r="V59" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
         <v>0</v>
@@ -6516,13 +6516,13 @@
         <v>32</v>
       </c>
       <c r="J60" t="n">
-        <v>2.436029411764706</v>
+        <v>4.615625</v>
       </c>
       <c r="K60" t="n">
-        <v>0.6146003286802253</v>
+        <v>0.2418563535623059</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -6546,13 +6546,13 @@
         <v>32</v>
       </c>
       <c r="T60" t="n">
-        <v>4.615625</v>
+        <v>2.436029411764706</v>
       </c>
       <c r="U60" t="n">
-        <v>0.2418563535623059</v>
+        <v>0.6146003286802253</v>
       </c>
       <c r="V60" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
         <v>0</v>
@@ -6591,13 +6591,13 @@
         <v>32</v>
       </c>
       <c r="J61" t="n">
-        <v>2.963786764705882</v>
+        <v>4.624816176470588</v>
       </c>
       <c r="K61" t="n">
-        <v>0.6739307313032494</v>
+        <v>0.2611578979284513</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -6621,13 +6621,13 @@
         <v>32</v>
       </c>
       <c r="T61" t="n">
-        <v>4.624816176470588</v>
+        <v>2.963786764705882</v>
       </c>
       <c r="U61" t="n">
-        <v>0.2611578979284513</v>
+        <v>0.6739307313032494</v>
       </c>
       <c r="V61" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>32</v>
       </c>
       <c r="J62" t="n">
-        <v>3.254779411764706</v>
+        <v>4.748713235294118</v>
       </c>
       <c r="K62" t="n">
-        <v>0.5281334715047229</v>
+        <v>0.1654175083217664</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -6696,13 +6696,13 @@
         <v>32</v>
       </c>
       <c r="T62" t="n">
-        <v>4.748713235294118</v>
+        <v>3.254779411764706</v>
       </c>
       <c r="U62" t="n">
-        <v>0.1654175083217664</v>
+        <v>0.5281334715047229</v>
       </c>
       <c r="V62" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
         <v>0</v>
@@ -6741,13 +6741,13 @@
         <v>32</v>
       </c>
       <c r="J63" t="n">
-        <v>3.179595588235294</v>
+        <v>4.789154411764706</v>
       </c>
       <c r="K63" t="n">
-        <v>0.6332685826997735</v>
+        <v>0.1315937269561732</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -6771,13 +6771,13 @@
         <v>32</v>
       </c>
       <c r="T63" t="n">
-        <v>4.789154411764706</v>
+        <v>3.179595588235294</v>
       </c>
       <c r="U63" t="n">
-        <v>0.1315937269561732</v>
+        <v>0.6332685826997735</v>
       </c>
       <c r="V63" t="n">
-        <v>0.9375</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
         <v>0</v>
@@ -6816,13 +6816,13 @@
         <v>32</v>
       </c>
       <c r="J64" t="n">
-        <v>3.509191176470588</v>
+        <v>4.791544117647058</v>
       </c>
       <c r="K64" t="n">
-        <v>0.5693318147252965</v>
+        <v>0.1571806057643267</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -6846,13 +6846,13 @@
         <v>32</v>
       </c>
       <c r="T64" t="n">
-        <v>4.791544117647058</v>
+        <v>3.509191176470588</v>
       </c>
       <c r="U64" t="n">
-        <v>0.1571806057643267</v>
+        <v>0.5693318147252965</v>
       </c>
       <c r="V64" t="n">
-        <v>0.9375</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
         <v>0</v>
@@ -6891,16 +6891,16 @@
         <v>32</v>
       </c>
       <c r="J65" t="n">
-        <v>3.535477941176471</v>
+        <v>4.815992647058824</v>
       </c>
       <c r="K65" t="n">
-        <v>0.4821226005651124</v>
+        <v>0.2854871679047686</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>0.96875</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>0.03125</v>
       </c>
       <c r="N65" t="n">
         <v>32</v>
@@ -6921,16 +6921,16 @@
         <v>32</v>
       </c>
       <c r="T65" t="n">
-        <v>4.815992647058824</v>
+        <v>3.535477941176471</v>
       </c>
       <c r="U65" t="n">
-        <v>0.2854871679047686</v>
+        <v>0.4821226005651124</v>
       </c>
       <c r="V65" t="n">
-        <v>0.96875</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>0.03125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -6966,16 +6966,16 @@
         <v>32</v>
       </c>
       <c r="J66" t="n">
-        <v>3.557536764705882</v>
+        <v>4.860110294117647</v>
       </c>
       <c r="K66" t="n">
-        <v>0.5031228172167828</v>
+        <v>0.1141973779551122</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>0.96875</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>0.03125</v>
       </c>
       <c r="N66" t="n">
         <v>32</v>
@@ -6996,16 +6996,16 @@
         <v>32</v>
       </c>
       <c r="T66" t="n">
-        <v>4.860110294117647</v>
+        <v>3.557536764705882</v>
       </c>
       <c r="U66" t="n">
-        <v>0.1141973779551122</v>
+        <v>0.5031228172167828</v>
       </c>
       <c r="V66" t="n">
-        <v>0.96875</v>
+        <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>0.03125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -7041,16 +7041,16 @@
         <v>32</v>
       </c>
       <c r="J67" t="n">
-        <v>3.529963235294118</v>
+        <v>4.865625</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4430721054959355</v>
+        <v>0.1027700868827943</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>0.96875</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>0.03125</v>
       </c>
       <c r="N67" t="n">
         <v>32</v>
@@ -7071,16 +7071,16 @@
         <v>32</v>
       </c>
       <c r="T67" t="n">
-        <v>4.865625</v>
+        <v>3.529963235294118</v>
       </c>
       <c r="U67" t="n">
-        <v>0.1027700868827943</v>
+        <v>0.4430721054959355</v>
       </c>
       <c r="V67" t="n">
-        <v>0.96875</v>
+        <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>0.03125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -7116,16 +7116,16 @@
         <v>32</v>
       </c>
       <c r="J68" t="n">
-        <v>3.66452205882353</v>
+        <v>4.904411764705882</v>
       </c>
       <c r="K68" t="n">
-        <v>0.364633904799764</v>
+        <v>0.04783515243246884</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>0.09375</v>
       </c>
       <c r="N68" t="n">
         <v>32</v>
@@ -7146,16 +7146,16 @@
         <v>32</v>
       </c>
       <c r="T68" t="n">
-        <v>4.904411764705882</v>
+        <v>3.66452205882353</v>
       </c>
       <c r="U68" t="n">
-        <v>0.04783515243246884</v>
+        <v>0.364633904799764</v>
       </c>
       <c r="V68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>0.09375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -7191,13 +7191,13 @@
         <v>32</v>
       </c>
       <c r="J69" t="n">
-        <v>2.070404411764706</v>
+        <v>4.125</v>
       </c>
       <c r="K69" t="n">
-        <v>0.7347504394189667</v>
+        <v>0.889583279146416</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>0.3125</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -7221,13 +7221,13 @@
         <v>32</v>
       </c>
       <c r="T69" t="n">
-        <v>4.125</v>
+        <v>2.070404411764706</v>
       </c>
       <c r="U69" t="n">
-        <v>0.889583279146416</v>
+        <v>0.7347504394189667</v>
       </c>
       <c r="V69" t="n">
-        <v>0.3125</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
         <v>0</v>
@@ -7266,13 +7266,13 @@
         <v>32</v>
       </c>
       <c r="J70" t="n">
-        <v>2.272794117647059</v>
+        <v>4.439522058823529</v>
       </c>
       <c r="K70" t="n">
-        <v>0.8248143269604059</v>
+        <v>0.4308642596145489</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>0.46875</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -7296,13 +7296,13 @@
         <v>32</v>
       </c>
       <c r="T70" t="n">
-        <v>4.439522058823529</v>
+        <v>2.272794117647059</v>
       </c>
       <c r="U70" t="n">
-        <v>0.4308642596145489</v>
+        <v>0.8248143269604059</v>
       </c>
       <c r="V70" t="n">
-        <v>0.46875</v>
+        <v>0</v>
       </c>
       <c r="W70" t="n">
         <v>0</v>
@@ -7341,13 +7341,13 @@
         <v>32</v>
       </c>
       <c r="J71" t="n">
-        <v>2.262867647058823</v>
+        <v>4.559375</v>
       </c>
       <c r="K71" t="n">
-        <v>0.72565667055928</v>
+        <v>0.3637539126582913</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>0.6875</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -7371,13 +7371,13 @@
         <v>32</v>
       </c>
       <c r="T71" t="n">
-        <v>4.559375</v>
+        <v>2.262867647058823</v>
       </c>
       <c r="U71" t="n">
-        <v>0.3637539126582913</v>
+        <v>0.72565667055928</v>
       </c>
       <c r="V71" t="n">
-        <v>0.6875</v>
+        <v>0</v>
       </c>
       <c r="W71" t="n">
         <v>0</v>
@@ -7416,13 +7416,13 @@
         <v>32</v>
       </c>
       <c r="J72" t="n">
-        <v>2.718933823529412</v>
+        <v>4.646875</v>
       </c>
       <c r="K72" t="n">
-        <v>0.7127085096626161</v>
+        <v>0.2296402519784363</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>0.78125</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -7446,13 +7446,13 @@
         <v>32</v>
       </c>
       <c r="T72" t="n">
-        <v>4.646875</v>
+        <v>2.718933823529412</v>
       </c>
       <c r="U72" t="n">
-        <v>0.2296402519784363</v>
+        <v>0.7127085096626161</v>
       </c>
       <c r="V72" t="n">
-        <v>0.78125</v>
+        <v>0</v>
       </c>
       <c r="W72" t="n">
         <v>0</v>
@@ -7491,13 +7491,13 @@
         <v>32</v>
       </c>
       <c r="J73" t="n">
-        <v>2.872610294117647</v>
+        <v>4.723161764705882</v>
       </c>
       <c r="K73" t="n">
-        <v>0.7106835601124675</v>
+        <v>0.1837155280454133</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>0.90625</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -7521,13 +7521,13 @@
         <v>32</v>
       </c>
       <c r="T73" t="n">
-        <v>4.723161764705882</v>
+        <v>2.872610294117647</v>
       </c>
       <c r="U73" t="n">
-        <v>0.1837155280454133</v>
+        <v>0.7106835601124675</v>
       </c>
       <c r="V73" t="n">
-        <v>0.90625</v>
+        <v>0</v>
       </c>
       <c r="W73" t="n">
         <v>0</v>
@@ -7566,13 +7566,13 @@
         <v>32</v>
       </c>
       <c r="J74" t="n">
-        <v>3.095404411764706</v>
+        <v>4.755330882352942</v>
       </c>
       <c r="K74" t="n">
-        <v>0.6822608954062974</v>
+        <v>0.1906033410217714</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>0.90625</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -7596,13 +7596,13 @@
         <v>32</v>
       </c>
       <c r="T74" t="n">
-        <v>4.755330882352942</v>
+        <v>3.095404411764706</v>
       </c>
       <c r="U74" t="n">
-        <v>0.1906033410217714</v>
+        <v>0.6822608954062974</v>
       </c>
       <c r="V74" t="n">
-        <v>0.90625</v>
+        <v>0</v>
       </c>
       <c r="W74" t="n">
         <v>0</v>
@@ -7641,13 +7641,13 @@
         <v>32</v>
       </c>
       <c r="J75" t="n">
-        <v>2.98547794117647</v>
+        <v>4.743198529411766</v>
       </c>
       <c r="K75" t="n">
-        <v>0.7592609897329067</v>
+        <v>0.2030661792232378</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -7671,13 +7671,13 @@
         <v>32</v>
       </c>
       <c r="T75" t="n">
-        <v>4.743198529411766</v>
+        <v>2.98547794117647</v>
       </c>
       <c r="U75" t="n">
-        <v>0.2030661792232378</v>
+        <v>0.7592609897329067</v>
       </c>
       <c r="V75" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="W75" t="n">
         <v>0</v>
@@ -7716,16 +7716,16 @@
         <v>32</v>
       </c>
       <c r="J76" t="n">
-        <v>3.251286764705883</v>
+        <v>4.840624999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>0.7250777687100405</v>
+        <v>0.09345544286619781</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>0.03125</v>
       </c>
       <c r="N76" t="n">
         <v>32</v>
@@ -7746,16 +7746,16 @@
         <v>32</v>
       </c>
       <c r="T76" t="n">
-        <v>4.840624999999999</v>
+        <v>3.251286764705883</v>
       </c>
       <c r="U76" t="n">
-        <v>0.09345544286619781</v>
+        <v>0.7250777687100405</v>
       </c>
       <c r="V76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0.03125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -7791,13 +7791,13 @@
         <v>32</v>
       </c>
       <c r="J77" t="n">
-        <v>3.295220588235294</v>
+        <v>4.844852941176471</v>
       </c>
       <c r="K77" t="n">
-        <v>0.6673352932152704</v>
+        <v>0.07987251254947882</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -7821,13 +7821,13 @@
         <v>32</v>
       </c>
       <c r="T77" t="n">
-        <v>4.844852941176471</v>
+        <v>3.295220588235294</v>
       </c>
       <c r="U77" t="n">
-        <v>0.07987251254947882</v>
+        <v>0.6673352932152704</v>
       </c>
       <c r="V77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W77" t="n">
         <v>0</v>
@@ -7866,16 +7866,16 @@
         <v>32</v>
       </c>
       <c r="J78" t="n">
-        <v>3.379595588235294</v>
+        <v>4.855514705882353</v>
       </c>
       <c r="K78" t="n">
-        <v>0.7914770693317933</v>
+        <v>0.1699749329857475</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>0.96875</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>0.03125</v>
       </c>
       <c r="N78" t="n">
         <v>32</v>
@@ -7896,16 +7896,16 @@
         <v>32</v>
       </c>
       <c r="T78" t="n">
-        <v>4.855514705882353</v>
+        <v>3.379595588235294</v>
       </c>
       <c r="U78" t="n">
-        <v>0.1699749329857475</v>
+        <v>0.7914770693317933</v>
       </c>
       <c r="V78" t="n">
-        <v>0.96875</v>
+        <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>0.03125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -7941,16 +7941,16 @@
         <v>32</v>
       </c>
       <c r="J79" t="n">
-        <v>3.706433823529412</v>
+        <v>4.861397058823529</v>
       </c>
       <c r="K79" t="n">
-        <v>0.707402473540615</v>
+        <v>0.1557753562116211</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="N79" t="n">
         <v>32</v>
@@ -7971,16 +7971,16 @@
         <v>32</v>
       </c>
       <c r="T79" t="n">
-        <v>4.861397058823529</v>
+        <v>3.706433823529412</v>
       </c>
       <c r="U79" t="n">
-        <v>0.1557753562116211</v>
+        <v>0.707402473540615</v>
       </c>
       <c r="V79" t="n">
-        <v>0.9375</v>
+        <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
